--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260611.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260611.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>3,385,000</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>3,385,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,537,384</t>
+          <t>5,616,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>5,616,000</t>
+          <t>1,537,384</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>4,480,578</t>
+          <t>371,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>371,000</t>
+          <t>4,480,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,189,076</t>
+          <t>91,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>829,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>1,189,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>91,000</t>
+          <t>829,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>328,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
